--- a/src/main/resources/python/MultifacetedModeling/DataOutput/KNN/avg_classes.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/DataOutput/KNN/avg_classes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="result0" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="result0" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,88 +455,88 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.07832746865857546</t>
+          <t>0.08082284807887678</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0664884343830016</t>
+          <t>0.09895408526045475</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.9333336663968619</t>
+          <t>0.8542109778623171</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0.07417426628525618</t>
+          <t>0.07847362411285015</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.10487035630879851</t>
+          <t>0.06567463247610851</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.835477690012562</t>
+          <t>0.9350449106701454</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0.08011810392237505</t>
+          <t>0.07572079021727454</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.10222777679177256</t>
+          <t>0.10637088326080699</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.8443037382243022</t>
+          <t>0.8312248774841997</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0.07171350752618472</t>
+          <t>0.07202479612891496</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.07388598409866032</t>
+          <t>0.07433266422814754</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.9173036423579046</t>
+          <t>0.9163995307675178</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
     </row>
